--- a/data/data_raw/eurostat/AT_cars_road_eqs_carpda.xlsx
+++ b/data/data_raw/eurostat/AT_cars_road_eqs_carpda.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,72 +451,62 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -544,41 +534,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>4641308</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4694921</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4748048</v>
+      </c>
       <c r="I2" t="n">
-        <v>4641308</v>
+        <v>4821557</v>
       </c>
       <c r="J2" t="n">
-        <v>4694921</v>
+        <v>4898578</v>
       </c>
       <c r="K2" t="n">
-        <v>4748048</v>
+        <v>4978852</v>
       </c>
       <c r="L2" t="n">
-        <v>4821557</v>
+        <v>5039548</v>
       </c>
       <c r="M2" t="n">
-        <v>4898578</v>
+        <v>5091827</v>
       </c>
       <c r="N2" t="n">
-        <v>4978852</v>
+        <v>5133836</v>
       </c>
       <c r="O2" t="n">
-        <v>5039548</v>
+        <v>5150890</v>
       </c>
       <c r="P2" t="n">
-        <v>5091827</v>
+        <v>5185006</v>
       </c>
       <c r="Q2" t="n">
-        <v>5133836</v>
-      </c>
-      <c r="R2" t="n">
-        <v>5150890</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5185006</v>
+        <v>5231893</v>
       </c>
     </row>
     <row r="3">
@@ -605,41 +595,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>2013748</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2023336</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2033924</v>
+      </c>
       <c r="I3" t="n">
-        <v>2013748</v>
+        <v>2056715</v>
       </c>
       <c r="J3" t="n">
-        <v>2023336</v>
+        <v>2106473</v>
       </c>
       <c r="K3" t="n">
-        <v>2033924</v>
+        <v>2173325</v>
       </c>
       <c r="L3" t="n">
-        <v>2056715</v>
+        <v>2224880</v>
       </c>
       <c r="M3" t="n">
-        <v>2106473</v>
+        <v>2264561</v>
       </c>
       <c r="N3" t="n">
-        <v>2173325</v>
+        <v>2305984</v>
       </c>
       <c r="O3" t="n">
-        <v>2224880</v>
+        <v>2342409</v>
       </c>
       <c r="P3" t="n">
-        <v>2264561</v>
+        <v>2383807</v>
       </c>
       <c r="Q3" t="n">
-        <v>2305984</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2342409</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2383807</v>
+        <v>2444088</v>
       </c>
     </row>
     <row r="4">
@@ -666,41 +656,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="5">
@@ -727,41 +717,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>2621588</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2663654</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2703999</v>
+      </c>
       <c r="I5" t="n">
-        <v>2621588</v>
+        <v>2750383</v>
       </c>
       <c r="J5" t="n">
-        <v>2663654</v>
+        <v>2771925</v>
       </c>
       <c r="K5" t="n">
-        <v>2703999</v>
+        <v>2778795</v>
       </c>
       <c r="L5" t="n">
-        <v>2750383</v>
+        <v>2779026</v>
       </c>
       <c r="M5" t="n">
-        <v>2771925</v>
+        <v>2776651</v>
       </c>
       <c r="N5" t="n">
-        <v>2778795</v>
+        <v>2745471</v>
       </c>
       <c r="O5" t="n">
-        <v>2779026</v>
+        <v>2692682</v>
       </c>
       <c r="P5" t="n">
-        <v>2776651</v>
+        <v>2640528</v>
       </c>
       <c r="Q5" t="n">
-        <v>2745471</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2692682</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2640528</v>
+        <v>2582446</v>
       </c>
     </row>
     <row r="6">
@@ -788,41 +778,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>2219</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2397</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2475</v>
+      </c>
       <c r="I6" t="n">
-        <v>2219</v>
+        <v>2457</v>
       </c>
       <c r="J6" t="n">
-        <v>2397</v>
+        <v>2433</v>
       </c>
       <c r="K6" t="n">
-        <v>2475</v>
+        <v>2365</v>
       </c>
       <c r="L6" t="n">
-        <v>2457</v>
+        <v>2602</v>
       </c>
       <c r="M6" t="n">
-        <v>2433</v>
+        <v>2753</v>
       </c>
       <c r="N6" t="n">
-        <v>2365</v>
+        <v>2654</v>
       </c>
       <c r="O6" t="n">
-        <v>2602</v>
+        <v>2564</v>
       </c>
       <c r="P6" t="n">
-        <v>2753</v>
+        <v>2342</v>
       </c>
       <c r="Q6" t="n">
-        <v>2654</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2564</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2342</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -849,41 +839,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>2070</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3386</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5032</v>
+      </c>
       <c r="I7" t="n">
-        <v>2070</v>
+        <v>9073</v>
       </c>
       <c r="J7" t="n">
-        <v>3386</v>
+        <v>14618</v>
       </c>
       <c r="K7" t="n">
-        <v>5032</v>
+        <v>20831</v>
       </c>
       <c r="L7" t="n">
-        <v>9073</v>
+        <v>29523</v>
       </c>
       <c r="M7" t="n">
-        <v>14618</v>
+        <v>44507</v>
       </c>
       <c r="N7" t="n">
-        <v>20831</v>
+        <v>76539</v>
       </c>
       <c r="O7" t="n">
-        <v>29523</v>
+        <v>110225</v>
       </c>
       <c r="P7" t="n">
-        <v>44507</v>
+        <v>155490</v>
       </c>
       <c r="Q7" t="n">
-        <v>76539</v>
-      </c>
-      <c r="R7" t="n">
-        <v>110225</v>
-      </c>
-      <c r="S7" t="n">
-        <v>155490</v>
+        <v>200603</v>
       </c>
     </row>
     <row r="8">
@@ -910,41 +900,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>5972</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7931</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10125</v>
+      </c>
       <c r="I8" t="n">
-        <v>5972</v>
+        <v>14459</v>
       </c>
       <c r="J8" t="n">
-        <v>7931</v>
+        <v>20180</v>
       </c>
       <c r="K8" t="n">
-        <v>10125</v>
+        <v>26732</v>
       </c>
       <c r="L8" t="n">
-        <v>14459</v>
+        <v>35642</v>
       </c>
       <c r="M8" t="n">
-        <v>20180</v>
+        <v>50615</v>
       </c>
       <c r="N8" t="n">
-        <v>26732</v>
+        <v>82381</v>
       </c>
       <c r="O8" t="n">
-        <v>35642</v>
+        <v>115799</v>
       </c>
       <c r="P8" t="n">
-        <v>50615</v>
+        <v>160671</v>
       </c>
       <c r="Q8" t="n">
-        <v>82381</v>
-      </c>
-      <c r="R8" t="n">
-        <v>115799</v>
-      </c>
-      <c r="S8" t="n">
-        <v>160671</v>
+        <v>205359</v>
       </c>
     </row>
     <row r="9">
@@ -971,41 +961,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>2003699</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2011104</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2019139</v>
+      </c>
       <c r="I9" t="n">
-        <v>2003699</v>
+        <v>2038019</v>
       </c>
       <c r="J9" t="n">
-        <v>2011104</v>
+        <v>2080434</v>
       </c>
       <c r="K9" t="n">
-        <v>2019139</v>
+        <v>2139239</v>
       </c>
       <c r="L9" t="n">
-        <v>2038019</v>
+        <v>2179235</v>
       </c>
       <c r="M9" t="n">
-        <v>2080434</v>
+        <v>2195578</v>
       </c>
       <c r="N9" t="n">
-        <v>2139239</v>
+        <v>2197006</v>
       </c>
       <c r="O9" t="n">
-        <v>2179235</v>
+        <v>2194125</v>
       </c>
       <c r="P9" t="n">
-        <v>2195578</v>
+        <v>2188368</v>
       </c>
       <c r="Q9" t="n">
-        <v>2197006</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2194125</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2188368</v>
+        <v>2186500</v>
       </c>
     </row>
     <row r="10">
@@ -1032,41 +1022,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>9664</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11505</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13327</v>
+      </c>
       <c r="I10" t="n">
-        <v>9664</v>
+        <v>16531</v>
       </c>
       <c r="J10" t="n">
-        <v>11505</v>
+        <v>22290</v>
       </c>
       <c r="K10" t="n">
-        <v>13327</v>
+        <v>28619</v>
       </c>
       <c r="L10" t="n">
-        <v>16531</v>
+        <v>37897</v>
       </c>
       <c r="M10" t="n">
-        <v>22290</v>
+        <v>54472</v>
       </c>
       <c r="N10" t="n">
-        <v>28619</v>
+        <v>81745</v>
       </c>
       <c r="O10" t="n">
-        <v>37897</v>
+        <v>109361</v>
       </c>
       <c r="P10" t="n">
-        <v>54472</v>
+        <v>141980</v>
       </c>
       <c r="Q10" t="n">
-        <v>81745</v>
-      </c>
-      <c r="R10" t="n">
-        <v>109361</v>
-      </c>
-      <c r="S10" t="n">
-        <v>141980</v>
+        <v>188324</v>
       </c>
     </row>
     <row r="11">
@@ -1093,41 +1083,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>385</v>
+      </c>
+      <c r="G11" t="n">
+        <v>727</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1458</v>
+      </c>
       <c r="I11" t="n">
-        <v>385</v>
+        <v>2165</v>
       </c>
       <c r="J11" t="n">
-        <v>727</v>
+        <v>3749</v>
       </c>
       <c r="K11" t="n">
-        <v>1458</v>
+        <v>5467</v>
       </c>
       <c r="L11" t="n">
-        <v>2165</v>
+        <v>7748</v>
       </c>
       <c r="M11" t="n">
-        <v>3749</v>
+        <v>14511</v>
       </c>
       <c r="N11" t="n">
-        <v>5467</v>
+        <v>27233</v>
       </c>
       <c r="O11" t="n">
-        <v>7748</v>
+        <v>38923</v>
       </c>
       <c r="P11" t="n">
-        <v>14511</v>
+        <v>53459</v>
       </c>
       <c r="Q11" t="n">
-        <v>27233</v>
-      </c>
-      <c r="R11" t="n">
-        <v>38923</v>
-      </c>
-      <c r="S11" t="n">
-        <v>53459</v>
+        <v>69264</v>
       </c>
     </row>
     <row r="12">
@@ -1154,41 +1144,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>2621133</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2663063</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2702922</v>
+      </c>
       <c r="I12" t="n">
-        <v>2621133</v>
+        <v>2749046</v>
       </c>
       <c r="J12" t="n">
-        <v>2663063</v>
+        <v>2770470</v>
       </c>
       <c r="K12" t="n">
-        <v>2702922</v>
+        <v>2776332</v>
       </c>
       <c r="L12" t="n">
-        <v>2749046</v>
+        <v>2772854</v>
       </c>
       <c r="M12" t="n">
-        <v>2770470</v>
+        <v>2762273</v>
       </c>
       <c r="N12" t="n">
-        <v>2776332</v>
+        <v>2717475</v>
       </c>
       <c r="O12" t="n">
-        <v>2772854</v>
+        <v>2651280</v>
       </c>
       <c r="P12" t="n">
-        <v>2762273</v>
+        <v>2584985</v>
       </c>
       <c r="Q12" t="n">
-        <v>2717475</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2651280</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2584985</v>
+        <v>2510099</v>
       </c>
     </row>
     <row r="13">
@@ -1215,41 +1205,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>432</v>
+      </c>
+      <c r="G13" t="n">
+        <v>542</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1028</v>
+      </c>
       <c r="I13" t="n">
-        <v>432</v>
+        <v>1224</v>
       </c>
       <c r="J13" t="n">
-        <v>542</v>
+        <v>1268</v>
       </c>
       <c r="K13" t="n">
-        <v>1028</v>
+        <v>2220</v>
       </c>
       <c r="L13" t="n">
-        <v>1224</v>
+        <v>5878</v>
       </c>
       <c r="M13" t="n">
-        <v>1268</v>
+        <v>13652</v>
       </c>
       <c r="N13" t="n">
-        <v>2220</v>
+        <v>26208</v>
       </c>
       <c r="O13" t="n">
-        <v>5878</v>
+        <v>38745</v>
       </c>
       <c r="P13" t="n">
-        <v>13652</v>
+        <v>52138</v>
       </c>
       <c r="Q13" t="n">
-        <v>26208</v>
-      </c>
-      <c r="R13" t="n">
-        <v>38745</v>
-      </c>
-      <c r="S13" t="n">
-        <v>52138</v>
+        <v>66843</v>
       </c>
     </row>
     <row r="14">
@@ -1276,41 +1266,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G14" t="n">
+        <v>49</v>
+      </c>
+      <c r="H14" t="n">
+        <v>49</v>
+      </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="J14" t="n">
-        <v>49</v>
+        <v>187</v>
       </c>
       <c r="K14" t="n">
-        <v>49</v>
+        <v>243</v>
       </c>
       <c r="L14" t="n">
-        <v>113</v>
+        <v>294</v>
       </c>
       <c r="M14" t="n">
-        <v>187</v>
+        <v>726</v>
       </c>
       <c r="N14" t="n">
-        <v>243</v>
+        <v>1788</v>
       </c>
       <c r="O14" t="n">
-        <v>294</v>
+        <v>2657</v>
       </c>
       <c r="P14" t="n">
-        <v>726</v>
+        <v>3405</v>
       </c>
       <c r="Q14" t="n">
-        <v>1788</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2657</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3405</v>
+        <v>5504</v>
       </c>
     </row>
     <row r="15">
@@ -1337,41 +1327,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L15" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="M15" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="N15" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="O15" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="P15" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="Q15" t="n">
-        <v>55</v>
-      </c>
-      <c r="R15" t="n">
         <v>62</v>
-      </c>
-      <c r="S15" t="n">
-        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -1398,24 +1388,24 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1443,24 +1433,24 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1488,41 +1478,41 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>1682</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2144</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2611</v>
+      </c>
       <c r="I18" t="n">
-        <v>1682</v>
+        <v>2915</v>
       </c>
       <c r="J18" t="n">
-        <v>2144</v>
+        <v>3108</v>
       </c>
       <c r="K18" t="n">
-        <v>2611</v>
+        <v>3510</v>
       </c>
       <c r="L18" t="n">
-        <v>2915</v>
+        <v>3474</v>
       </c>
       <c r="M18" t="n">
-        <v>3108</v>
+        <v>3308</v>
       </c>
       <c r="N18" t="n">
-        <v>3510</v>
+        <v>3132</v>
       </c>
       <c r="O18" t="n">
-        <v>3474</v>
+        <v>2947</v>
       </c>
       <c r="P18" t="n">
-        <v>3308</v>
+        <v>2771</v>
       </c>
       <c r="Q18" t="n">
-        <v>3132</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2947</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2771</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="19">
@@ -1549,9 +1539,15 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -1577,12 +1573,6 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
         <v>0</v>
       </c>
     </row>
